--- a/data/trans_dic/P05B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P05B_R-Provincia-trans_dic.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,6</t>
+          <t>0,89; 5,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,26</t>
+          <t>0,96; 5,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,97</t>
+          <t>3,09; 8,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,68</t>
+          <t>0,39; 3,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,87</t>
+          <t>1,63; 6,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,94</t>
+          <t>2,66; 7,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,39</t>
+          <t>0,87; 3,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,47</t>
+          <t>1,56; 4,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,24</t>
+          <t>3,54; 7,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,27 +824,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,67</t>
+          <t>2,24; 5,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,36</t>
+          <t>3,17; 7,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,41</t>
+          <t>1,43; 4,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,26</t>
+          <t>0,24; 2,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,74</t>
+          <t>3,79; 7,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,0</t>
+          <t>2,41; 6,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,18</t>
+          <t>3,18; 6,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,54</t>
+          <t>0,24; 1,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,97</t>
+          <t>3,4; 6,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,14</t>
+          <t>3,29; 5,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,17</t>
+          <t>2,6; 5,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,53</t>
+          <t>0,32; 1,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,45</t>
+          <t>2,07; 6,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,82</t>
+          <t>2,03; 6,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 9,4</t>
+          <t>4,1; 9,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,54</t>
+          <t>1,59; 5,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,11</t>
+          <t>3,6; 6,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,88</t>
+          <t>0,14; 1,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,38</t>
+          <t>2,13; 4,89</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,85</t>
+          <t>1,34; 4,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,27</t>
+          <t>0,53; 2,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,57</t>
+          <t>0,47; 2,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,86</t>
+          <t>1,27; 5,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,72</t>
+          <t>1,44; 4,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,98</t>
+          <t>0,81; 3,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,98</t>
+          <t>1,55; 5,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,24</t>
+          <t>1,42; 3,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,18</t>
+          <t>1,74; 4,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,91</t>
+          <t>0,97; 2,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,72</t>
+          <t>1,25; 3,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,59</t>
+          <t>1,61; 3,72</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 11,74</t>
+          <t>4,45; 11,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,24</t>
+          <t>0,89; 5,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 14,18</t>
+          <t>6,34; 14,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,65</t>
+          <t>0,91; 5,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,86</t>
+          <t>0,4; 3,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 11,5</t>
+          <t>6,18; 11,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,63</t>
+          <t>1,43; 4,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,91</t>
+          <t>0,21; 1,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,21</t>
+          <t>0,32; 2,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,17</t>
+          <t>0,71; 4,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,54</t>
+          <t>0,3; 2,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,82</t>
+          <t>0,72; 2,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,54</t>
+          <t>0,17; 1,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,06</t>
+          <t>0,33; 1,83</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,34</t>
+          <t>1,13; 3,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,72</t>
+          <t>0,28; 1,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,63</t>
+          <t>0,49; 2,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,59</t>
+          <t>0,26; 1,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,84</t>
+          <t>4,64; 8,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,06</t>
+          <t>0,27; 2,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,99</t>
+          <t>0,91; 2,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,68</t>
+          <t>1,21; 2,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,47</t>
+          <t>3,19; 5,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,47</t>
+          <t>0,36; 1,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,28</t>
+          <t>0,91; 2,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,87</t>
+          <t>0,87; 2,06</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,09</t>
+          <t>1,52; 4,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,06</t>
+          <t>0,4; 2,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,05</t>
+          <t>0,14; 1,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,33</t>
+          <t>2,55; 5,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,41</t>
+          <t>0,25; 1,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,7</t>
+          <t>0,29; 1,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,41</t>
+          <t>0,28; 1,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,12</t>
+          <t>2,35; 4,15</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,51</t>
+          <t>0,45; 1,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,06</t>
+          <t>0,26; 1,01</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,99</t>
+          <t>0,32; 1,03</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,61</t>
+          <t>2,42; 3,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,17</t>
+          <t>1,23; 2,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,86</t>
+          <t>0,98; 1,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,61</t>
+          <t>0,8; 1,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,43</t>
+          <t>4,0; 5,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,09</t>
+          <t>1,22; 2,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,75</t>
+          <t>1,67; 2,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,59</t>
+          <t>0,99; 1,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,35</t>
+          <t>3,38; 4,35</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,97</t>
+          <t>1,35; 2,03</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,1</t>
+          <t>1,45; 2,13</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,42</t>
+          <t>0,95; 1,43</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>716</t>
         </is>
       </c>
     </row>
@@ -2209,37 +2209,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2361; 15280</t>
+          <t>2419; 14376</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2617; 15289</t>
+          <t>2794; 14722</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9081; 26263</t>
+          <t>9042; 25334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>0; 3773</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1017; 9600</t>
+          <t>1016; 8452</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4958; 16471</t>
+          <t>4578; 17176</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8376; 22919</t>
+          <t>7674; 22870</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4485; 18089</t>
+          <t>4645; 19735</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9543; 25535</t>
+          <t>8943; 26248</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20572; 42103</t>
+          <t>20595; 42760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4130</t>
+          <t>0; 4696</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8126</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10468; 27943</t>
+          <t>11029; 29476</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15427; 37212</t>
+          <t>16040; 37667</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7159; 22140</t>
+          <t>7170; 22261</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1244; 11660</t>
+          <t>1289; 11628</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18818; 38984</t>
+          <t>19077; 38823</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12859; 31298</t>
+          <t>12549; 31892</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16342; 37543</t>
+          <t>16655; 36440</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1398; 7910</t>
+          <t>1331; 8445</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32458; 59494</t>
+          <t>33946; 61436</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33121; 63031</t>
+          <t>33834; 60961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27244; 53001</t>
+          <t>26675; 54198</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3753; 15732</t>
+          <t>3420; 15456</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22612</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6142; 20514</t>
+          <t>6588; 19428</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2635,52 +2635,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 9343</t>
+          <t>0; 8865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6130; 21442</t>
+          <t>6347; 21341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13869; 31526</t>
+          <t>13764; 32509</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4970</t>
+          <t>0; 4899</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7041</t>
+          <t>0; 8032</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6057; 19242</t>
+          <t>5628; 18340</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23916; 46442</t>
+          <t>23549; 44889</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5886</t>
+          <t>0; 4947</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>899; 12281</t>
+          <t>901; 10263</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15082; 35588</t>
+          <t>14223; 32615</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>19165</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4687; 17391</t>
+          <t>4808; 17914</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2018; 12227</t>
+          <t>1993; 11021</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1706; 9452</t>
+          <t>1731; 9685</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4239; 18269</t>
+          <t>4739; 18797</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5591; 17542</t>
+          <t>5367; 17643</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3990; 15443</t>
+          <t>3156; 15180</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6368; 22751</t>
+          <t>5902; 21297</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4796; 15317</t>
+          <t>5929; 15805</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11565; 30511</t>
+          <t>12700; 30453</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7417; 22179</t>
+          <t>7375; 21688</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9506; 27853</t>
+          <t>9348; 26882</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11220; 28194</t>
+          <t>12779; 29413</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>716</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>339</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1055</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8969; 23858</t>
+          <t>9047; 24042</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1853; 11137</t>
+          <t>1889; 10873</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3482</t>
+          <t>0; 3581</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12700; 29219</t>
+          <t>13065; 29258</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2748; 14597</t>
+          <t>1992; 12986</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>886; 8437</t>
+          <t>875; 8468</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1603</t>
+          <t>0; 1696</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25156; 47074</t>
+          <t>25285; 47894</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5779; 20033</t>
+          <t>6164; 19967</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>875; 8206</t>
+          <t>883; 8463</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3584</t>
+          <t>0; 4511</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4449</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>879; 8682</t>
+          <t>872; 8038</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6911</t>
+          <t>0; 6111</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4170</t>
+          <t>0; 4596</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7414</t>
+          <t>0; 7632</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1915; 11604</t>
+          <t>1967; 11813</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6483</t>
+          <t>0; 6686</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 5086</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>895; 6520</t>
+          <t>790; 5901</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3918; 15457</t>
+          <t>3958; 15846</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>954; 8513</t>
+          <t>955; 8403</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6069</t>
+          <t>0; 5973</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1795; 10852</t>
+          <t>1763; 9779</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>19914</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6886; 20507</t>
+          <t>6914; 21221</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1797; 11375</t>
+          <t>1850; 10633</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3935; 17111</t>
+          <t>3167; 16266</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1254; 9923</t>
+          <t>1882; 12221</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31371; 56418</t>
+          <t>29622; 55193</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1776; 14256</t>
+          <t>1871; 14019</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6271; 20499</t>
+          <t>6242; 19946</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5795; 22692</t>
+          <t>9267; 22400</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>41291; 68456</t>
+          <t>39966; 69617</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4898; 19884</t>
+          <t>4890; 19587</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11867; 30515</t>
+          <t>12147; 31254</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9210; 27486</t>
+          <t>12935; 30658</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>9436</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11941; 30330</t>
+          <t>11235; 30720</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2987; 15864</t>
+          <t>3100; 17135</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6639</t>
+          <t>0; 6682</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>724; 9773</t>
+          <t>1130; 9752</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19538; 41756</t>
+          <t>19991; 40658</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2053; 11563</t>
+          <t>2026; 11980</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2342; 14068</t>
+          <t>2363; 14300</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1881; 10083</t>
+          <t>2320; 11130</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>34513; 62865</t>
+          <t>35778; 63264</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7593; 24072</t>
+          <t>7136; 24322</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3946; 16961</t>
+          <t>4099; 16268</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3659; 16224</t>
+          <t>5145; 16714</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>45413</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>85473</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>77821; 118038</t>
+          <t>79226; 119159</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>42992; 73995</t>
+          <t>42094; 72273</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33487; 62825</t>
+          <t>33076; 61293</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25729; 55549</t>
+          <t>28070; 53861</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>135783; 183332</t>
+          <t>135032; 183299</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42825; 73961</t>
+          <t>43147; 74619</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59492; 97187</t>
+          <t>58836; 94563</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>33726; 59068</t>
+          <t>36797; 60395</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>224001; 289091</t>
+          <t>225037; 289010</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>93701; 137168</t>
+          <t>94193; 141390</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>100222; 145077</t>
+          <t>100422; 147346</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>65425; 101869</t>
+          <t>68745; 103457</t>
         </is>
       </c>
     </row>
